--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -47,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,28 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,16 +774,16 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -810,13 +795,13 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -828,10 +813,10 @@
       <c r="P4" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -843,10 +828,10 @@
       <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -874,16 +859,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -895,14 +880,14 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>20.4</v>
+      <c r="M5" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -913,10 +898,10 @@
       <c r="P5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -926,19 +911,19 @@
         <v>78</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="V5" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>10</v>
@@ -957,18 +942,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -980,13 +965,13 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -998,10 +983,10 @@
       <c r="P6" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1013,10 +998,10 @@
       <c r="U6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1044,16 +1029,16 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1065,16 +1050,16 @@
       <c r="J7" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1083,10 +1068,10 @@
       <c r="P7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1098,10 +1083,10 @@
       <c r="U7" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1127,18 +1112,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="E8" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1150,43 +1135,43 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>54.8</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1196,7 +1181,7 @@
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1214,16 +1199,16 @@
       <c r="C9" s="3" t="n">
         <v>1783.6</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>161.7</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>107.4</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>134.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1235,13 +1220,13 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="8" t="n">
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1253,10 +1238,10 @@
       <c r="P9" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" s="16" t="n">
-        <v>255.6</v>
-      </c>
-      <c r="R9" s="9" t="n">
+      <c r="Q9" s="9" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="R9" s="8" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1268,10 +1253,10 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1281,7 +1266,7 @@
         <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.8</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1299,20 +1284,20 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1321,12 +1306,12 @@
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1336,12 +1321,12 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q10" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1351,12 +1336,12 @@
         <v>61.6</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1382,36 +1367,36 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+      <c r="H11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1423,10 +1408,10 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1438,10 +1423,10 @@
       <c r="U11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1467,39 +1452,39 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1508,10 +1493,10 @@
       <c r="P12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1520,20 +1505,20 @@
       <c r="T12" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="8" t="n">
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>173.2</v>
+        <v>73.2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>11.1</v>
@@ -1554,37 +1539,37 @@
       <c r="C13" s="3" t="n">
         <v>230.1</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1593,10 +1578,10 @@
       <c r="P13" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1608,10 +1593,10 @@
       <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1621,7 +1606,7 @@
         <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1639,37 +1624,37 @@
       <c r="C14" s="3" t="n">
         <v>121.4</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
@@ -1678,10 +1663,10 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1693,20 +1678,20 @@
       <c r="U14" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>185.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1722,18 +1707,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2340.8</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1743,18 +1728,18 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
@@ -1763,10 +1748,10 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1778,11 +1763,11 @@
       <c r="U15" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="17" t="n">
-        <v>41.9</v>
+      <c r="W15" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.3</v>
@@ -1809,20 +1794,20 @@
       <c r="C16" s="3" t="n">
         <v>1530.8</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="G16" s="9" t="n">
+      <c r="E16" s="8" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1830,13 +1815,13 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="8" t="n">
         <v>102.9</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>101.9</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1848,10 +1833,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1863,10 +1848,10 @@
       <c r="U16" s="3" t="n">
         <v>76.3</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="8" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1876,7 +1861,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>142.3</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1892,18 +1877,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1916,12 +1901,12 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1933,25 +1918,25 @@
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1977,18 +1962,18 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="D18" s="9" t="n">
+        <v>332</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -2000,28 +1985,28 @@
       <c r="J18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.7</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2030,13 +2015,13 @@
       <c r="T18" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="8" t="n">
+      <c r="U18" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2046,7 +2031,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2062,18 +2047,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2085,16 +2070,16 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
@@ -2103,10 +2088,10 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2118,13 +2103,13 @@
       <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2149,37 +2134,37 @@
       <c r="C20" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>118.4</v>
+      <c r="H20" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="N20" s="8" t="n">
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2188,10 +2173,10 @@
       <c r="P20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2203,10 +2188,10 @@
       <c r="U20" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2232,21 +2217,21 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="9" t="n">
+      <c r="E21" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2255,28 +2240,28 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2288,17 +2273,17 @@
       <c r="U21" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>1844.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>5.4</v>
@@ -2319,37 +2304,37 @@
       <c r="C22" s="3" t="n">
         <v>294.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>167.4</v>
+      <c r="G22" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2358,32 +2343,32 @@
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
+        <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.3</v>
@@ -2404,16 +2389,16 @@
       <c r="C23" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>96.2</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>125.8</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2425,13 +2410,13 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="16" t="n">
+      <c r="M23" s="8" t="n">
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2443,10 +2428,10 @@
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2458,10 +2443,10 @@
       <c r="U23" s="3" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2471,7 +2456,7 @@
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>126.5</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2489,16 +2474,16 @@
       <c r="C24" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2511,12 +2496,12 @@
         <v>3.7</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2528,25 +2513,25 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W24" s="9" t="n">
+      <c r="V24" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2556,7 +2541,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.3</v>
+        <v>25.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2574,34 +2559,34 @@
       <c r="C25" s="3" t="n">
         <v>177.8</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="17" t="n">
+      <c r="L25" s="10" t="n">
         <v>40.6</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2613,10 +2598,10 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2628,10 +2613,10 @@
       <c r="U25" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2657,21 +2642,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>345</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2680,13 +2665,13 @@
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2698,10 +2683,10 @@
       <c r="P26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2713,10 +2698,10 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2744,34 +2729,34 @@
       <c r="C27" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="n">
+      <c r="F27" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2783,10 +2768,10 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2798,14 +2783,14 @@
       <c r="U27" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2829,16 +2814,16 @@
       <c r="C28" s="3" t="n">
         <v>282.4</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2850,14 +2835,14 @@
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>29.9</v>
+      <c r="M28" s="8" t="n">
+        <v>19.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
@@ -2868,10 +2853,10 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2883,20 +2868,20 @@
       <c r="U28" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="X28" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2914,16 +2899,16 @@
       <c r="C29" s="3" t="n">
         <v>146.2</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2935,13 +2920,13 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2953,10 +2938,10 @@
       <c r="P29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2968,10 +2953,10 @@
       <c r="U29" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2981,7 +2966,7 @@
         <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2997,36 +2982,36 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>1156.5</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="G30" s="17" t="n">
-        <v>25.7</v>
+      <c r="G30" s="8" t="n">
+        <v>56.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1171.8</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="K30" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="16" t="n">
+      <c r="L30" s="9" t="n">
         <v>102.2</v>
       </c>
-      <c r="M30" s="16" t="n">
+      <c r="M30" s="8" t="n">
         <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3038,14 +3023,14 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>13.5</v>
+        <v>135.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3053,17 +3038,17 @@
       <c r="U30" s="3" t="n">
         <v>68.8</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="8" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>2411.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3084,16 +3069,16 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3103,30 +3088,30 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3135,16 +3120,16 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="V31" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W31" s="9" t="n">
+      <c r="U31" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
@@ -3169,34 +3154,34 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3208,13 +3193,13 @@
       <c r="P32" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
@@ -3223,20 +3208,20 @@
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X32" s="8" t="n">
+      <c r="W32" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>181.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3254,16 +3239,16 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3275,16 +3260,16 @@
       <c r="J33" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L33" s="9" t="n">
+      <c r="K33" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
@@ -3293,25 +3278,25 @@
       <c r="P33" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>183.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3337,37 +3322,37 @@
       <c r="C34" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="8" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
@@ -3376,10 +3361,10 @@
       <c r="P34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3391,10 +3376,10 @@
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3422,19 +3407,19 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3443,17 +3428,17 @@
       <c r="J35" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="8" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>13.9</v>
+      <c r="N35" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3461,35 +3446,35 @@
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>25.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="X35" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>185.8</v>
+        <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3505,22 +3490,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="9" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>119</v>
+      <c r="G36" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3528,16 +3513,16 @@
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
@@ -3546,10 +3531,10 @@
       <c r="P36" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3561,17 +3546,17 @@
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>194.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.3</v>
@@ -3592,17 +3577,17 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="17" t="n">
-        <v>14.3</v>
+      <c r="G37" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3613,13 +3598,13 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3629,12 +3614,12 @@
         <v>495</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3646,10 +3631,10 @@
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="16" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3675,21 +3660,21 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
@@ -3699,12 +3684,12 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3716,32 +3701,32 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V38" s="16" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W38" s="9" t="n">
+      <c r="V38" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>15.6</v>
@@ -3760,36 +3745,36 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.8</v>
+        <v>10.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3801,32 +3786,32 @@
       <c r="P39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V39" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>172.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>0</v>
@@ -3847,23 +3832,23 @@
       <c r="C40" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="E40" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.1</v>
@@ -3871,13 +3856,13 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M40" s="9" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N40" s="8" t="n">
+      <c r="M40" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
@@ -3886,25 +3871,25 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3914,7 +3899,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>120.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3932,32 +3917,32 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L41" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3969,32 +3954,32 @@
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
+        <v>70.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>841.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>6.7</v>
@@ -4015,23 +4000,23 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>2.9</v>
@@ -4039,13 +4024,13 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4054,10 +4039,10 @@
       <c r="P42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4069,10 +4054,10 @@
       <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4082,7 +4067,7 @@
         <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4100,23 +4085,23 @@
       <c r="C43" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>8.6</v>
+      <c r="G43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4124,28 +4109,28 @@
       <c r="K43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q43" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4154,13 +4139,13 @@
       <c r="U43" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="8" t="n">
+      <c r="X43" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="Y43" s="3" t="n">
@@ -4185,26 +4170,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="14" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4222,19 +4207,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1423.4</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>802.1</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>1127.8</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>19.1</v>
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
@@ -4243,15 +4228,15 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="K45" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="M45" s="16" t="n">
+      <c r="M45" s="9" t="n">
         <v>102.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4261,12 +4246,12 @@
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4276,13 +4261,13 @@
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="V45" s="16" t="n">
-        <v>1234</v>
-      </c>
-      <c r="W45" s="16" t="n">
-        <v>219</v>
+        <v>66</v>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="W45" s="8" t="n">
+        <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>138.1</v>
@@ -4291,7 +4276,7 @@
         <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4309,34 +4294,34 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4348,14 +4333,14 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="16" t="n">
-        <v>2.4</v>
+      <c r="R46" s="8" t="n">
+        <v>24.5</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>68.3</v>
@@ -4363,20 +4348,20 @@
       <c r="U46" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.5</v>
+        <v>78.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>78.7</v>
+        <v>7.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
